--- a/data/PlayMode.xlsx
+++ b/data/PlayMode.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,13 +443,10 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>MatchMode 枚举值（proto/match/match_service.proto）：1=5V5 3=1V1 4=PVE_SOLO 5=PVE_TEAM 6=PVP_CHALLENGE</t>
+          <t>MatchMode 枚举值（proto/match/match_service.proto）：1=5V5 3=1V1 4=PVE_SOLO 5=PVE_TEAM 6=PVP_CHALLENGE 7=PVP_TEAM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -459,12 +456,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>是否开放。改成 false 后新入队被拒，排队中的票由池写者撤掉</t>
+          <t>是否开放。改成 false 后新入队被拒，排队中的票不再续命，最长一个探测有效期后过期出队</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PVE_SOLO 填 1；PVE_TEAM 填人数上限（实际上限再与 Dungeon.max_team_size、引擎每队上限 5 取小）；其它模式填 0</t>
+          <t>PVE_SOLO 填 1；PVE_TEAM 填同场人数上限（再与 Dungeon.max_team_size、引擎每队上限 5 取小）；PVP_TEAM 填每侧人数上限（1..5）；其它模式填 0</t>
         </is>
       </c>
     </row>
@@ -551,6 +548,23 @@
       </c>
       <c r="E10" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
